--- a/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
@@ -1559,19 +1559,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1669,7 +1669,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1743,13 +1743,13 @@
         <v>30.82224430000005</v>
       </c>
       <c r="N4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="O4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="P4" t="n">
-        <v>5.790863699999997</v>
+        <v>5.790863699999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0285</v>
@@ -1761,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>26.28542482500007</v>
+        <v>26.28542482500006</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1799,22 +1799,22 @@
         <v>195.5</v>
       </c>
       <c r="F5" t="n">
-        <v>244.9923875000001</v>
+        <v>244.9923875</v>
       </c>
       <c r="G5" t="n">
-        <v>195.4999999999999</v>
+        <v>195.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8521474347826091</v>
+        <v>0.8521474347826088</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>42.50761249999988</v>
+        <v>42.50761249999996</v>
       </c>
       <c r="K5" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>30.82224430000005</v>
@@ -1826,7 +1826,7 @@
         <v>261.7714</v>
       </c>
       <c r="O5" t="n">
-        <v>216.7714000000001</v>
+        <v>216.7714</v>
       </c>
       <c r="P5" t="n">
         <v>2.6012568</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="6">
@@ -1879,22 +1879,22 @@
         <v>241.5</v>
       </c>
       <c r="F6" t="n">
-        <v>298.9901408</v>
+        <v>298.9901408000001</v>
       </c>
       <c r="G6" t="n">
-        <v>241.5</v>
+        <v>241.4999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8124732086956522</v>
+        <v>0.8124732086956523</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>69.00985919999999</v>
+        <v>69.00985919999994</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>332.6215999999999</v>
+        <v>332.6216</v>
       </c>
       <c r="O6" t="n">
         <v>302.6216</v>
@@ -1912,7 +1912,7 @@
         <v>3.631459200000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01200000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="R6" t="n">
         <v>45.36986301369863</v>
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-5.684341886080801e-14</v>
       </c>
     </row>
     <row r="7">
@@ -1959,19 +1959,19 @@
         <v>287.5</v>
       </c>
       <c r="F7" t="n">
-        <v>390.0000572000001</v>
+        <v>390.0000572</v>
       </c>
       <c r="G7" t="n">
         <v>287.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8695653449275365</v>
+        <v>0.8695653449275363</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>58.49994279999987</v>
+        <v>58.49994279999993</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         <v>394.7369</v>
       </c>
       <c r="P7" t="n">
-        <v>4.736842799999999</v>
+        <v>4.7368428</v>
       </c>
       <c r="Q7" t="n">
         <v>0.012</v>
@@ -8620,10 +8620,10 @@
         <v>161.7714</v>
       </c>
       <c r="M18" t="n">
-        <v>161.7714000000001</v>
+        <v>161.7714</v>
       </c>
       <c r="N18" t="n">
-        <v>161.7714000000001</v>
+        <v>161.7714</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -10126,13 +10126,13 @@
         <v>2038</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8521474347826091</v>
+        <v>0.8521474347826088</v>
       </c>
       <c r="J2" t="n">
         <v>0.97</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1178525652173908</v>
+        <v>0.1178525652173912</v>
       </c>
     </row>
     <row r="3">
@@ -10165,13 +10165,13 @@
         <v>2039</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8124732086956522</v>
+        <v>0.8124732086956523</v>
       </c>
       <c r="J3" t="n">
         <v>0.97</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1575267913043478</v>
+        <v>0.1575267913043477</v>
       </c>
     </row>
     <row r="4">
@@ -10204,13 +10204,13 @@
         <v>2040</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8695653449275365</v>
+        <v>0.8695653449275363</v>
       </c>
       <c r="J4" t="n">
         <v>0.97</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1004346550724635</v>
+        <v>0.1004346550724636</v>
       </c>
     </row>
     <row r="5">
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0.99</v>
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.99</v>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.8521474347826091</v>
+        <v>0.8521474347826088</v>
       </c>
       <c r="G11" t="n">
         <v>0.97</v>
@@ -10885,7 +10885,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.8124732086956522</v>
+        <v>0.8124732086956523</v>
       </c>
       <c r="G12" t="n">
         <v>0.97</v>
@@ -10930,7 +10930,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8695653449275365</v>
+        <v>0.8695653449275363</v>
       </c>
       <c r="G13" t="n">
         <v>0.97</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.01200000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="G36" t="n">
         <v>0.02</v>
@@ -22176,7 +22176,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>170.0174144999997</v>
+        <v>170.0174144999998</v>
       </c>
     </row>
     <row r="9">
@@ -22196,7 +22196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="10">
@@ -22216,7 +22216,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.187277024199952</v>
+        <v>8.187277024199954</v>
       </c>
     </row>
     <row r="11">
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.621510345540626</v>
+        <v>6.621510345540627</v>
       </c>
     </row>
     <row r="12">
@@ -22256,7 +22256,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.8124732086956522</v>
+        <v>0.8124732086956523</v>
       </c>
     </row>
     <row r="13">
@@ -22276,7 +22276,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9999999999999997</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -22376,7 +22376,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>467.6336700000001</v>
+        <v>467.63367</v>
       </c>
     </row>
     <row r="19">

--- a/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>3 / 3 / 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -774,7 +918,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -789,7 +933,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -807,7 +951,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -822,7 +966,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -839,7 +983,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -854,7 +998,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -871,7 +1015,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -886,7 +1030,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -903,7 +1047,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -918,7 +1062,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -935,7 +1079,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -950,7 +1094,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -967,7 +1111,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -982,7 +1126,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -999,7 +1143,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1014,7 +1158,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1175,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1046,7 +1190,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1207,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1078,7 +1222,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1239,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1110,7 +1254,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1271,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1142,7 +1286,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1303,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1174,7 +1318,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1335,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1206,7 +1350,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1367,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1238,7 +1382,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1399,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,7 +1414,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1431,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1302,7 +1446,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1463,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1334,7 +1478,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1495,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1366,7 +1510,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1527,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1398,7 +1542,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10263,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2038: total service level 0.8521 &lt; 0.97 (shortage 42.508 t) [guideline in this scenario]</t>
+          <t>2038: общий уровень сервиса 0.8521 &lt; 0.97 (дефицит 42.508 т) [в этом сценарии — ориентир, не жёсткое ограничение]</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10158,7 +10302,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2039: total service level 0.8125 &lt; 0.97 (shortage 69.010 t) [guideline in this scenario]</t>
+          <t>2039: общий уровень сервиса 0.8125 &lt; 0.97 (дефицит 69.010 т) [в этом сценарии — ориентир, не жёсткое ограничение]</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10197,7 +10341,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2040: total service level 0.8696 &lt; 0.97 (shortage 58.500 t) [guideline in this scenario]</t>
+          <t>2040: общий уровень сервиса 0.8696 &lt; 0.97 (дефицит 58.500 т) [в этом сценарии — ориентир, не жёсткое ограничение]</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10236,7 +10380,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2038-01: physical stock 30.822 t &lt; 45-day reserve 35.445 t</t>
+          <t>2038-01: физический запас 30.822 т &lt; 45-дневного резерва 35.445 т</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -10278,7 +10422,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2039-01: physical stock 0.000 t &lt; 45-day reserve 45.370 t</t>
+          <t>2039-01: физический запас 0.000 т &lt; 45-дневного резерва 45.370 т</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -10320,7 +10464,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2040-01: physical stock 0.000 t &lt; 45-day reserve 55.295 t</t>
+          <t>2040-01: физический запас 0.000 т &lt; 45-дневного резерва 55.295 т</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -11717,7 +11861,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11730,7 +11874,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11910,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11779,7 +11923,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11959,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11828,7 +11972,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11864,7 +12008,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11877,7 +12021,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11913,7 +12057,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11926,7 +12070,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11962,7 +12106,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11975,7 +12119,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -14123,7 +14267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M143"/>
+  <dimension ref="A1:N143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14192,6 +14336,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14247,6 +14396,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14302,6 +14456,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14357,6 +14516,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14412,6 +14576,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14467,6 +14636,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14522,6 +14696,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14577,6 +14756,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14632,6 +14816,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14687,6 +14876,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14742,6 +14936,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14797,6 +14996,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14852,6 +15056,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14907,6 +15116,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14962,6 +15176,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15017,6 +15236,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15072,6 +15296,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15127,6 +15356,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15182,6 +15416,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15237,6 +15476,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15292,6 +15536,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15347,6 +15596,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15402,6 +15656,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15457,6 +15716,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15512,6 +15776,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15567,6 +15836,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15622,6 +15896,11 @@
       <c r="M27" t="b">
         <v>1</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15677,6 +15956,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15732,6 +16016,11 @@
       <c r="M29" t="b">
         <v>1</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15787,6 +16076,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15842,6 +16136,11 @@
       <c r="M31" t="b">
         <v>1</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15897,6 +16196,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15952,6 +16256,11 @@
       <c r="M33" t="b">
         <v>1</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16007,6 +16316,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16062,6 +16376,11 @@
       <c r="M35" t="b">
         <v>1</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -16117,6 +16436,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16172,6 +16496,11 @@
       <c r="M37" t="b">
         <v>1</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -16227,6 +16556,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16282,6 +16616,11 @@
       <c r="M39" t="b">
         <v>1</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16337,6 +16676,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16392,6 +16736,11 @@
       <c r="M41" t="b">
         <v>1</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16447,6 +16796,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16502,6 +16856,11 @@
       <c r="M43" t="b">
         <v>1</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -16557,6 +16916,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16612,6 +16976,11 @@
       <c r="M45" t="b">
         <v>1</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16667,6 +17036,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16722,6 +17096,11 @@
       <c r="M47" t="b">
         <v>1</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16777,6 +17156,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16832,6 +17216,11 @@
       <c r="M49" t="b">
         <v>1</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16887,6 +17276,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16942,6 +17336,11 @@
       <c r="M51" t="b">
         <v>1</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -16997,6 +17396,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17052,6 +17456,11 @@
       <c r="M53" t="b">
         <v>1</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17107,6 +17516,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17162,6 +17576,11 @@
       <c r="M55" t="b">
         <v>1</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17217,6 +17636,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17272,6 +17696,11 @@
       <c r="M57" t="b">
         <v>1</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17327,6 +17756,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17382,6 +17816,11 @@
       <c r="M59" t="b">
         <v>1</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17437,6 +17876,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17492,6 +17936,11 @@
       <c r="M61" t="b">
         <v>1</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -17547,6 +17996,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17602,6 +18056,11 @@
       <c r="M63" t="b">
         <v>1</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17657,6 +18116,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17712,6 +18176,11 @@
       <c r="M65" t="b">
         <v>1</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17767,6 +18236,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17822,6 +18296,11 @@
       <c r="M67" t="b">
         <v>1</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17877,6 +18356,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17932,6 +18416,11 @@
       <c r="M69" t="b">
         <v>1</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -17987,6 +18476,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18042,6 +18536,11 @@
       <c r="M71" t="b">
         <v>1</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18097,6 +18596,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18152,6 +18656,11 @@
       <c r="M73" t="b">
         <v>1</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18207,6 +18716,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18262,6 +18776,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18317,6 +18836,11 @@
       <c r="M76" t="b">
         <v>1</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18372,6 +18896,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18427,6 +18956,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18482,6 +19016,11 @@
       <c r="M79" t="b">
         <v>1</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18537,6 +19076,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18592,6 +19136,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18647,6 +19196,11 @@
       <c r="M82" t="b">
         <v>1</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -18702,6 +19256,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18757,6 +19316,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18812,6 +19376,11 @@
       <c r="M85" t="b">
         <v>1</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -18867,6 +19436,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -18922,6 +19496,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -18977,6 +19556,11 @@
       <c r="M88" t="b">
         <v>1</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -19032,6 +19616,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -19087,6 +19676,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -19142,6 +19736,11 @@
       <c r="M91" t="b">
         <v>1</v>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -19197,6 +19796,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19252,6 +19856,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19307,6 +19916,11 @@
       <c r="M94" t="b">
         <v>1</v>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19362,6 +19976,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19417,6 +20036,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19472,6 +20096,11 @@
       <c r="M97" t="b">
         <v>1</v>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -19527,6 +20156,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -19582,6 +20216,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19637,6 +20276,11 @@
       <c r="M100" t="b">
         <v>1</v>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19692,6 +20336,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19747,6 +20396,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19802,6 +20456,11 @@
       <c r="M103" t="b">
         <v>1</v>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19857,6 +20516,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19912,6 +20576,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19967,6 +20636,11 @@
       <c r="M106" t="b">
         <v>1</v>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -20022,6 +20696,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20077,6 +20756,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20132,6 +20816,11 @@
       <c r="M109" t="b">
         <v>1</v>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -20187,6 +20876,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20242,6 +20936,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -20297,6 +20996,11 @@
       <c r="M112" t="b">
         <v>1</v>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -20352,6 +21056,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -20407,6 +21116,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20462,6 +21176,11 @@
       <c r="M115" t="b">
         <v>1</v>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -20517,6 +21236,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20572,6 +21296,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20627,6 +21356,11 @@
       <c r="M118" t="b">
         <v>1</v>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -20682,6 +21416,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20737,6 +21476,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20792,6 +21536,11 @@
       <c r="M121" t="b">
         <v>1</v>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -20847,6 +21596,11 @@
       <c r="M122" t="b">
         <v>1</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20902,6 +21656,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20957,6 +21716,11 @@
       <c r="M124" t="b">
         <v>1</v>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -21012,6 +21776,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -21067,6 +21836,11 @@
       <c r="M126" t="b">
         <v>1</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -21122,6 +21896,11 @@
       <c r="M127" t="b">
         <v>1</v>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -21177,6 +21956,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21232,6 +22016,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -21287,6 +22076,11 @@
       <c r="M130" t="b">
         <v>1</v>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -21342,6 +22136,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21397,6 +22196,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21452,6 +22256,11 @@
       <c r="M133" t="b">
         <v>1</v>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -21507,6 +22316,11 @@
       <c r="M134" t="b">
         <v>1</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21562,6 +22376,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21617,6 +22436,11 @@
       <c r="M136" t="b">
         <v>1</v>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -21672,6 +22496,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21727,6 +22556,11 @@
       <c r="M138" t="b">
         <v>1</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -21782,6 +22616,11 @@
       <c r="M139" t="b">
         <v>1</v>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -21837,6 +22676,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -21892,6 +22736,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -21947,6 +22796,11 @@
       <c r="M142" t="b">
         <v>1</v>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -22001,6 +22855,11 @@
       </c>
       <c r="M143" t="b">
         <v>1</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +1543,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -11850,18 +11883,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11874,7 +11907,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11899,18 +11932,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11923,7 +11956,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11948,18 +11981,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11972,7 +12005,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11997,18 +12030,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -12021,7 +12054,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12046,18 +12079,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -12070,7 +12103,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12095,18 +12128,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -12119,7 +12152,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12312,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -12303,7 +12336,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12514,7 +12547,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -12538,7 +12571,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12749,11 +12782,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>30.82224430000005</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G48" t="n">
         <v>70</v>
@@ -12773,7 +12806,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13115,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -13106,7 +13139,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13415,7 +13448,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -13439,7 +13472,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13879,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -13870,7 +13903,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,6 +1575,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
@@ -7538,7 +7538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7647,6 +7647,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7722,6 +7727,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7797,6 +7805,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7872,6 +7883,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7947,6 +7961,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8022,6 +8039,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8097,6 +8117,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8172,6 +8195,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8247,6 +8273,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8322,6 +8351,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8397,6 +8429,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8472,6 +8507,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8547,6 +8585,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8622,6 +8663,9 @@
       <c r="U14" t="n">
         <v>1.97835</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8697,6 +8741,9 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8772,6 +8819,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8847,6 +8897,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8922,6 +8975,9 @@
       <c r="U18" t="n">
         <v>72.7974</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8997,6 +9053,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9072,6 +9131,9 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9147,6 +9209,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9222,6 +9287,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9297,6 +9365,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9372,6 +9443,9 @@
       <c r="U24" t="n">
         <v>3.3933</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9447,6 +9521,9 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9522,6 +9599,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9597,6 +9677,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9672,6 +9755,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9747,6 +9833,9 @@
       <c r="U29" t="n">
         <v>12.71055</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9822,6 +9911,9 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9897,6 +9989,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9970,6 +10065,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9984,7 +10082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10048,6 +10146,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10090,6 +10193,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10132,6 +10238,9 @@
       <c r="L3" t="n">
         <v>1250</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10174,6 +10283,9 @@
       <c r="L4" t="n">
         <v>1430</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10216,6 +10328,9 @@
       <c r="L5" t="n">
         <v>1430</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10258,6 +10373,9 @@
       <c r="L6" t="n">
         <v>1430</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10299,6 +10417,9 @@
       </c>
       <c r="L7" t="n">
         <v>1430</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23005,7 +23126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23443,11 +23564,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -23463,11 +23584,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -23483,11 +23604,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -23503,7 +23624,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -23523,11 +23644,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -23543,10 +23664,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23563,11 +23684,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>78</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -23583,10 +23704,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>72</v>
       </c>
     </row>

--- a/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_fixed_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -870,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,7 +1396,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1414,24 +1416,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1441,29 +1443,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1473,29 +1475,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1505,176 +1507,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2411,6 +2556,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2483,6 +2638,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2554,6 +2715,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2625,6 +2792,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2696,6 +2869,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2767,6 +2946,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2838,6 +3023,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2909,6 +3100,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2980,6 +3177,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3051,6 +3254,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3122,6 +3331,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3193,6 +3408,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3264,6 +3485,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3335,6 +3562,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3406,6 +3639,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3477,6 +3716,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3548,6 +3793,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3619,6 +3870,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3690,6 +3947,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3761,6 +4024,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3832,6 +4101,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3903,6 +4178,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3974,6 +4255,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4045,6 +4332,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4116,6 +4409,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4187,6 +4486,12 @@
         <v>1.415606307500004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.59530225000007</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4258,6 +4563,12 @@
         <v>1.435829962500004</v>
       </c>
       <c r="U27" t="n">
+        <v>39.93236316666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4329,6 +4640,12 @@
         <v>1.456053617500004</v>
       </c>
       <c r="U28" t="n">
+        <v>40.2694240833334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4400,6 +4717,12 @@
         <v>1.476277272500004</v>
       </c>
       <c r="U29" t="n">
+        <v>40.60648500000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4471,6 +4794,12 @@
         <v>1.496500927500004</v>
       </c>
       <c r="U30" t="n">
+        <v>40.94354591666674</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4542,6 +4871,12 @@
         <v>1.516724582500004</v>
       </c>
       <c r="U31" t="n">
+        <v>41.2806068333334</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4613,6 +4948,12 @@
         <v>1.553711264000004</v>
       </c>
       <c r="U32" t="n">
+        <v>42.17643530000007</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4684,6 +5025,12 @@
         <v>1.607460972000004</v>
       </c>
       <c r="U33" t="n">
+        <v>43.07226376666673</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4755,6 +5102,12 @@
         <v>1.661210680000003</v>
       </c>
       <c r="U34" t="n">
+        <v>43.96809223333339</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4826,6 +5179,12 @@
         <v>1.714960388000003</v>
       </c>
       <c r="U35" t="n">
+        <v>44.86392070000006</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4897,6 +5256,12 @@
         <v>1.768710096000003</v>
       </c>
       <c r="U36" t="n">
+        <v>45.75974916666672</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4968,6 +5333,12 @@
         <v>1.822459804000003</v>
       </c>
       <c r="U37" t="n">
+        <v>46.65557763333339</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5039,6 +5410,12 @@
         <v>1.530160016000003</v>
       </c>
       <c r="U38" t="n">
+        <v>44.14142290000005</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5110,6 +5487,12 @@
         <v>0.8918107320000032</v>
       </c>
       <c r="U39" t="n">
+        <v>33.50226816666672</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5181,6 +5564,12 @@
         <v>0.416481448000003</v>
       </c>
       <c r="U40" t="n">
+        <v>28.29711343333338</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5252,6 +5641,12 @@
         <v>0.1301634030000015</v>
       </c>
       <c r="U41" t="n">
+        <v>23.09195870000005</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5323,6 +5718,12 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5394,6 +5795,12 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5465,6 +5872,12 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5536,6 +5949,12 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5607,6 +6026,12 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5678,6 +6103,12 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5749,6 +6180,12 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5820,6 +6257,12 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
+        <v>18.7531786</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5891,6 +6334,12 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5962,6 +6411,12 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6033,6 +6488,12 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6104,6 +6565,12 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6175,6 +6642,12 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6246,6 +6719,12 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6317,6 +6796,12 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6388,6 +6873,12 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6459,6 +6950,12 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6530,6 +7027,12 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6601,6 +7104,12 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6672,6 +7181,12 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
+        <v>24.91584506666667</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6743,6 +7258,12 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6814,6 +7335,12 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6885,6 +7412,12 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6956,6 +7489,12 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7027,6 +7566,12 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7098,6 +7643,12 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7169,6 +7720,12 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7240,6 +7797,12 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7311,6 +7874,12 @@
         <v>0</v>
       </c>
       <c r="U70" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7382,6 +7951,12 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7453,6 +8028,12 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7524,6 +8105,12 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10173,7 +10760,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10182,13 +10769,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -10747,7 +11334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12573,7 +13160,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12581,14 +13168,14 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G39" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -12605,7 +13192,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12622,7 +13209,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -12630,14 +13217,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>109.876</v>
       </c>
       <c r="G40" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -12671,7 +13258,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12679,18 +13266,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I41" t="b">
         <v>1</v>
@@ -12700,7 +13288,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12715,7 +13307,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12723,7 +13315,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -12759,27 +13351,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -12789,11 +13380,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12808,7 +13395,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -12816,14 +13403,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G44" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -12840,7 +13427,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12857,7 +13444,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -12865,14 +13452,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G45" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -12889,7 +13476,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12906,7 +13493,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -12914,170 +13501,170 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G46" t="n">
+        <v>190</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G47" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46">
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48">
         <f>=</f>
         <v/>
       </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D49" t="n">
         <v>2036</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47">
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <f>=</f>
         <v/>
       </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>25.44727350000007</v>
-      </c>
-      <c r="G48" t="n">
-        <v>70</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>190</v>
-      </c>
-      <c r="G49" t="n">
-        <v>190</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13092,7 +13679,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -13100,14 +13687,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>190</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G50" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -13124,7 +13711,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13728,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -13149,14 +13736,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>13.189</v>
+        <v>41.2806068333334</v>
       </c>
       <c r="G51" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -13173,7 +13760,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13190,7 +13777,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -13198,14 +13785,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>13.1882</v>
+        <v>190</v>
       </c>
       <c r="G52" t="n">
-        <v>13.189</v>
+        <v>190</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -13222,7 +13809,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13239,7 +13826,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -13247,219 +13834,219 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>190</v>
+      </c>
+      <c r="G53" t="n">
+        <v>190</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="G54" t="n">
+        <v>110</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>13.1882</v>
+      </c>
+      <c r="G55" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53">
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56">
         <f>=</f>
         <v/>
       </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D57" t="n">
         <v>2037</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54">
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57">
         <f>=</f>
         <v/>
       </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>20.18308956666672</v>
-      </c>
-      <c r="G55" t="n">
-        <v>120</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2038-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="G56" t="n">
-        <v>190</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>161.7714</v>
-      </c>
-      <c r="G57" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13474,7 +14061,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -13482,11 +14069,11 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>120</v>
+        <v>20.18308956666672</v>
       </c>
       <c r="G58" t="n">
         <v>120</v>
@@ -13506,7 +14093,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13523,7 +14110,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -13531,14 +14118,14 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>44.14142290000005</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -13555,7 +14142,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13572,7 +14159,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -13580,268 +14167,268 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="G60" t="n">
+        <v>190</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>161.7714</v>
+      </c>
+      <c r="G61" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>120</v>
+      </c>
+      <c r="G62" t="n">
+        <v>120</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>100</v>
+      </c>
+      <c r="G63" t="n">
+        <v>100</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60">
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64">
         <f>=</f>
         <v/>
       </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D65" t="n">
         <v>2038</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61">
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65">
         <f>=</f>
         <v/>
       </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>120</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2039-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>190</v>
-      </c>
-      <c r="G63" t="n">
-        <v>190</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>190</v>
-      </c>
-      <c r="G64" t="n">
-        <v>190</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>22.622</v>
-      </c>
-      <c r="G65" t="n">
-        <v>110</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -13856,7 +14443,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -13864,14 +14451,14 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>22.6216</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>22.622</v>
+        <v>120</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -13888,7 +14475,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2039-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13905,7 +14492,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -13913,11 +14500,11 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>120</v>
+        <v>24.91584506666667</v>
       </c>
       <c r="G67" t="n">
         <v>120</v>
@@ -13937,7 +14524,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2039-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13954,7 +14541,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -13962,14 +14549,14 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G68" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -13986,7 +14573,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14003,7 +14590,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -14011,317 +14598,317 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>190</v>
+      </c>
+      <c r="G69" t="n">
+        <v>190</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>22.622</v>
+      </c>
+      <c r="G70" t="n">
+        <v>110</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>22.6216</v>
+      </c>
+      <c r="G71" t="n">
+        <v>22.622</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>120</v>
+      </c>
+      <c r="G72" t="n">
+        <v>120</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>120</v>
+      </c>
+      <c r="G73" t="n">
+        <v>120</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69">
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74">
         <f>=</f>
         <v/>
       </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D75" t="n">
         <v>2039</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70">
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75">
         <f>=</f>
         <v/>
       </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>120</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>2040-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>190</v>
-      </c>
-      <c r="G72" t="n">
-        <v>190</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>190</v>
-      </c>
-      <c r="G73" t="n">
-        <v>190</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>84.73699999999999</v>
-      </c>
-      <c r="G74" t="n">
-        <v>110</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>84.73690000000001</v>
-      </c>
-      <c r="G75" t="n">
-        <v>84.73699999999999</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -14336,7 +14923,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -14344,11 +14931,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>120</v>
@@ -14368,7 +14955,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14972,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -14393,11 +14980,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>120</v>
+        <v>32.50000476666667</v>
       </c>
       <c r="G77" t="n">
         <v>120</v>
@@ -14417,7 +15004,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14434,7 +15021,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -14442,72 +15029,366 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>190</v>
+      </c>
+      <c r="G78" t="n">
+        <v>190</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>190</v>
+      </c>
+      <c r="G79" t="n">
+        <v>190</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>84.73699999999999</v>
+      </c>
+      <c r="G80" t="n">
+        <v>110</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>84.73690000000001</v>
+      </c>
+      <c r="G81" t="n">
+        <v>84.73699999999999</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>120</v>
+      </c>
+      <c r="G82" t="n">
+        <v>120</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>120</v>
+      </c>
+      <c r="G83" t="n">
+        <v>120</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78">
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84">
         <f>=</f>
         <v/>
       </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D85" t="n">
         <v>2040</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79">
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85">
         <f>=</f>
         <v/>
       </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23126,7 +24007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23168,7 +24049,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11167.303283673</v>
+        <v>11167.673149443</v>
       </c>
     </row>
     <row r="3">
@@ -23188,7 +24069,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9031.624801025504</v>
+        <v>9031.994666795503</v>
       </c>
     </row>
     <row r="4">
@@ -23328,7 +24209,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.187277024199954</v>
+        <v>8.18754819024997</v>
       </c>
     </row>
     <row r="11">
@@ -23348,7 +24229,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.621510345540627</v>
+        <v>6.621781511590642</v>
       </c>
     </row>
     <row r="12">
@@ -23508,7 +24389,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47.19299367300009</v>
+        <v>47.56285944300009</v>
       </c>
     </row>
     <row r="20">
@@ -23624,11 +24505,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -23644,11 +24525,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -23664,11 +24545,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -23684,11 +24565,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -23704,11 +24585,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -23724,11 +24605,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>72</v>
+      <c r="D32" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
